--- a/Power BI/MDSCHEMA_MEASURES.xlsx
+++ b/Power BI/MDSCHEMA_MEASURES.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ksoszka-my.sharepoint.com/personal/kamil_soszka_ksoszka_onmicrosoft_com/Documents/Kamil Soszka Business Intelligence/Power BI/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_0A58AA8DC5968491FEE2F89199632CEF24EBA757" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A63CEE4A-F747-478C-8B77-483556B17302}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_0A58AA8DC5968491FEE2F8919929EC2F3A61A6AA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1826F0E9-AF27-4915-AB66-DB9C849CF610}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,7 +88,7 @@
     <t>DEFAULT_FORMAT_STRING</t>
   </si>
   <si>
-    <t>9a73862e-093e-40e1-9c13-2b3120196746</t>
+    <t>3dad7259-201f-49e9-856b-2648fbaca7cc</t>
   </si>
   <si>
     <t>Model</t>
@@ -796,16 +796,16 @@
 // Construct the birthday date for the current year (January 28th).
 VAR BirthdayThisYear =
     DATE ( CurrentYear, 01, 28 )
-// Calculate the number of days until or since the birthday.  This value will be positive if the birthday has passed, and negative if it is in the future.
+// Calculate the number of days until or since the birthday. This value will be positive if the birthday has passed, and negative if it is in the future.
 VAR Pct =
     SWITCH (
         TRUE (),
         TodayDate &gt;= BirthdayThisYear, // If today's date is on or after the birthday this year...
-            DATEDIFF (
-                BirthdayThisYear, // ...calculate the number of days *since* the birthday.
-                TodayDate,
-                DAY
-            ),
+        DATEDIFF (
+            BirthdayThisYear, // ...calculate the number of days *since* the birthday.
+            TodayDate,
+            DAY
+        ),
         DATEDIFF ( // Otherwise (today's date is before the birthday this year)...
             DATE ( CurrentYear - 1, 01, 28 ), // ...construct the birthday date for the *previous* year.
             TodayDate, // ...calculate the number of days *since* the birthday last year.
@@ -816,7 +816,7 @@
 // Relies on a measure "[Number of days]", which likely represents the total number of days in the current year.
 VAR Result =
     "Date of birth: " &amp; FORMAT ( BirthDate, "mm/dd/yyyy" ) &amp; " | " &amp; "+"
-    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" )
+    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" ) &amp; " (" &amp; "-" &amp; [Number of days] - Pct &amp; "D)"
 // Return the result string.
 RETURN
     Result</t>
@@ -848,23 +848,23 @@
     SWITCH (
         TRUE (),
         TodayDate &gt;= NovemberFirstThisYear,  // If today is on or after Nov 1st this year
-            DATEDIFF (
-                NovemberFirstLastYear,
-                TodayDate,
-                DAY
-            ),
+        DATEDIFF (
+            NovemberFirstLastYear,
+            TodayDate,
+            DAY
+        ),
         TodayDate &lt; NovemberFirstThisYear,   // If today is before Nov 1st this year
-            DATEDIFF (
-                NovemberFirstLastYear,
-                TodayDate,
-                DAY
-            )
+        DATEDIFF (
+            NovemberFirstLastYear,
+            TodayDate,
+            DAY
+        )
     )
 // Construct the result string, including the founding date and the percentage of the year passed (or remaining).
 // Relies on a measure "[Number of days]", which likely represents the total number of days in the current year.
 VAR Result =
     "Business: "&amp;FORMAT ( FoundingDate, "mm/dd/yyyy" ) &amp; " | " &amp; "+"
-    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" )
+    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" ) &amp; " (" &amp; "-" &amp; [Number of days] - Pct &amp; "D)"
 // Return the result string.
 RETURN
     Result</t>
@@ -896,23 +896,23 @@
     SWITCH (
         TRUE (),
         TodayDate &gt;= SeptemberFirstThisYear,  // If today is on or after Sep 1st this year
-            DATEDIFF (
-                SeptemberFirstLastYear,
-                TodayDate,
-                DAY
-            ),
+        DATEDIFF (
+            SeptemberFirstLastYear,
+            TodayDate,
+            DAY
+        ),
         TodayDate &lt; SeptemberFirstThisYear,   // If today is before Sep 1st this year
-            DATEDIFF (
-                SeptemberFirstLastYear,
-                TodayDate,
-                DAY
-            )
+        DATEDIFF (
+            SeptemberFirstLastYear,
+            TodayDate,
+            DAY
+        )
     )
 // Construct the result string, including the start date and the percentage of the year passed (or remaining).
 // Relies on a measure "[Number of days]", which likely represents the total number of days in the current year.
 VAR Result =
     "Experience: "&amp;FORMAT ( StartDate, "mm/dd/yyyy" ) &amp; " | " &amp; "+"
-    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" )
+    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" ) &amp; " (" &amp; "-" &amp; [Number of days] - Pct &amp; "D)"
 // Return the result string.
 RETURN
     Result</t>
@@ -941,11 +941,11 @@
     SWITCH (
         TRUE (),
         TodayDate &lt; FebruaryTwentyFifthThisYear, // If today's date is *before* February 25th of this year...
-            DATEDIFF (
-                DATE ( CurrentYear - 1, 02, 25 ), // ...calculate the number of days between February 25th of the *previous* year...
-                TodayDate, // ...and today. This will be a *positive* number.
-                DAY
-            ),
+        DATEDIFF (
+            DATE ( CurrentYear - 1, 02, 25 ), // ...calculate the number of days between February 25th of the *previous* year...
+            TodayDate, // ...and today. This will be a *positive* number.
+            DAY
+        ),
         DATEDIFF ( // Otherwise (today's date is *on or after* February 25th of this year)...
             FebruaryTwentyFifthThisYear, // ...calculate the number of days between February 25th of *this* year...
             TodayDate, // ...and today's date.
@@ -956,7 +956,7 @@
 // Relies on a measure "[Number of days]", which likely represents the total number of days in the current year.
 VAR Result =
     "PhD: "&amp;FORMAT ( DefenseDate, "mm/dd/yyyy" ) &amp; " | " &amp; "+"
-    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" )
+    &amp; FORMAT ( DIVIDE ( Pct, [Number of days] ), "0.00%" ) &amp; " (" &amp; "-" &amp; [Number of days] - Pct &amp; "D)"
 // Return the result string.
 RETURN
     Result</t>
@@ -1365,7 +1365,7 @@
   <dimension ref="A1:U23"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="36.21875" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.33203125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="15.77734375" hidden="1" customWidth="1"/>
     <col min="3" max="3" width="13.109375" hidden="1" customWidth="1"/>
     <col min="4" max="4" width="28.5546875" bestFit="1" customWidth="1"/>
